--- a/stories/arbres/ATOM-SEC.MAI.003-05.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Daphné est à la maison. Maman ouvre la porte du balcon. L'air sent les géraniums. Daphné reste avec l'adulte. C'est maman. Maman dit : on reste derrière la protection. Daphné pose les pieds au sol. Les pieds restent au sol. Elle sent le carrelage sous les chaussettes. La protection est devant elle. Daphné pose les mains sur la protection. Elle reste derrière la protection. Un papillon passe. Daphné dit : maman, le papillon. Maman est près d'elle. Parce que les pieds sont au sol, Daphné est calme. Elles regardent les pots. Les fleurs sont roses. Les pieds restent au sol. L'adulte est là.</t>
+          <t>Daphné est à la maison. Maman ouvre la porte du balcon. L'air sent les géraniums. Daphné reste avec l'adulte. C'est maman. On reste derrière la protection. Daphné pose les pieds au sol. Les pieds restent au sol. Elle sent le carrelage sous les chaussettes. La protection est devant elle. Daphné pose les mains sur la protection. Elle reste derrière la protection. Un papillon passe. Maman, le papillon. Maman est près d'elle. Parce que les pieds sont au sol, Daphné est calme. Elles regardent les pots. Les fleurs sont roses. Les pieds restent au sol. L'adulte est là.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Daphné est à la maison. Maman ouvre la porte du balcon. L'air sent les géraniums. Daphné reste avec l'adulte. C'est maman.
+maman|On reste derrière la protection.
+narrateur|Daphné pose les pieds au sol. Les pieds restent au sol. Elle sent le carrelage sous les chaussettes. La protection est devant elle. Daphné pose les mains sur la protection. Elle reste derrière la protection. Un papillon passe.
+enfant-f|Maman, le papillon. Maman est près d'elle. Parce que les pieds sont au sol, Daphné est calme.
+narrateur|Elles regardent les pots. Les fleurs sont roses. Les pieds restent au sol. L'adulte est là.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Daphné est au balcon. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Daphné a les pieds au sol. Elle est derrière la protection. Maman, l'adulte, est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1842,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Daphné et maman rentrent. Les pieds restent au sol.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2009,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2049,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-05.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Elles regardent les pots. Les fleurs sont roses. Les pieds restent au sol. L'adulte est là.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Daphné est au balcon. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1687,7 @@
           <t>narrateur|Daphné a les pieds au sol. Elle est derrière la protection. Maman, l'adulte, est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1847,6 +1859,7 @@
           <t>narrateur|Daphné et maman rentrent. Les pieds restent au sol.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2014,6 +2027,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2056,6 +2070,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2257,6 +2285,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.MAI.003-05.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Daphné au balcon avec maman</t>
+          <t>Les géraniums de Victorina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le carrelage est tiède. Victorina va au balcon avec maman. Un papillon passe près des géraniums roses. Pieds au sol, derrière la protection.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Daphné est à la maison. Maman ouvre la porte du balcon. L'air sent les géraniums. Daphné reste avec l'adulte. C'est maman. On reste derrière la protection. Daphné pose les pieds au sol. Les pieds restent au sol. Elle sent le carrelage sous les chaussettes. La protection est devant elle. Daphné pose les mains sur la protection. Elle reste derrière la protection. Un papillon passe. Maman, le papillon. Maman est près d'elle. Parce que les pieds sont au sol, Daphné est calme. Elles regardent les pots. Les fleurs sont roses. Les pieds restent au sol. L'adulte est là.</t>
+          <t>Le carrelage du salon est tiède. Le soleil a tout chauffé, tout doux. Une poussière d'or danse dans le rayon. Ça sent les géraniums, déjà. Les pots sont roses, près de la vitre. Une feuille a une petite goutte. Un grain de pollen brille, tout fin. Le rayon est jaune, tout chaud. Tu as senti les fleurs, Victorina ? Oui, maman. Ça sent fort. Les géraniums sont roses, aujourd'hui. En ce moment, maman ouvre la porte. L'air sent les géraniums, plus près. Victorina reste avec l'adulte. C'est maman. On reste derrière la protection. D'accord, maman. Victorina pose les pieds au sol. Les pieds restent au sol. Elle sent le carrelage sous les chaussettes. La protection est devant elle. Victorina pose les mains sur la protection. Elle reste derrière la protection. Bravo, Victorina. Tes pieds sont au sol. Un papillon passe, tout léger. Maman, le papillon. Je le vois. On le regarde ici, avec moi. Maman est près d'elle. Parce que les pieds sont au sol, Victorina est calme. Elles regardent les pots. Les fleurs sont roses. Les pieds restent au sol. Tu vois les pétales ? Oui. Ils sont roses. On reste avec l'adulte. Derrière la protection. Pieds au sol. Oui. C'est du bon travail. Tu as fini de regarder le papillon ? Il est encore là. Alors on reste un peu. Tu vois les pots roses ? Un, deux, trois. On les compte ici. Derrière la protection.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,61 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Daphné est à la maison. Maman ouvre la porte du balcon. L'air sent les géraniums. Daphné reste avec l'adulte. C'est maman.
+          <t>narrateur|Le carrelage du salon est tiède.
+narrateur|Le soleil a tout chauffé, tout doux.
+narrateur|Une poussière d'or danse dans le rayon.
+narrateur|Ça sent les géraniums, déjà.
+narrateur|Les pots sont roses, près de la vitre.
+narrateur|Une feuille a une petite goutte.
+narrateur|Un grain de pollen brille, tout fin.
+narrateur|Le rayon est jaune, tout chaud.
+maman|Tu as senti les fleurs, Victorina ?
+enfant-f|Oui, maman.
+enfant-f|Ça sent fort.
+maman|Les géraniums sont roses, aujourd'hui.
+narrateur|En ce moment, maman ouvre la porte.
+narrateur|L'air sent les géraniums, plus près.
+narrateur|Victorina reste avec l'adulte.
+narrateur|C'est maman.
 maman|On reste derrière la protection.
-narrateur|Daphné pose les pieds au sol. Les pieds restent au sol. Elle sent le carrelage sous les chaussettes. La protection est devant elle. Daphné pose les mains sur la protection. Elle reste derrière la protection. Un papillon passe.
-enfant-f|Maman, le papillon. Maman est près d'elle. Parce que les pieds sont au sol, Daphné est calme.
-narrateur|Elles regardent les pots. Les fleurs sont roses. Les pieds restent au sol. L'adulte est là.</t>
+enfant-f|D'accord, maman.
+narrateur|Victorina pose les pieds au sol.
+narrateur|Les pieds restent au sol.
+narrateur|Elle sent le carrelage sous les chaussettes.
+narrateur|La protection est devant elle.
+narrateur|Victorina pose les mains sur la protection.
+narrateur|Elle reste derrière la protection.
+maman|Bravo, Victorina.
+maman|Tes pieds sont au sol.
+narrateur|Un papillon passe, tout léger.
+enfant-f|Maman, le papillon.
+maman|Je le vois.
+maman|On le regarde ici, avec moi.
+narrateur|Maman est près d'elle.
+narrateur|Parce que les pieds sont au sol, Victorina est calme.
+narrateur|Elles regardent les pots.
+narrateur|Les fleurs sont roses.
+narrateur|Les pieds restent au sol.
+maman|Tu vois les pétales ?
+enfant-f|Oui.
+enfant-f|Ils sont roses.
+maman|On reste avec l'adulte.
+maman|Derrière la protection.
+enfant-f|Pieds au sol.
+maman|Oui.
+maman|C'est du bon travail.
+maman|Tu as fini de regarder le papillon ?
+enfant-f|Il est encore là.
+maman|Alors on reste un peu.
+maman|Tu vois les pots roses ?
+enfant-f|Un, deux, trois.
+maman|On les compte ici.
+maman|Derrière la protection.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>oiseau,fleurs</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1405,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Daphné est au balcon. Que fait-elle ?</t>
+          <t>Victorina est au balcon. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,7 +1565,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Daphné est au balcon. Que fait-elle ?</t>
+          <t>narrateur|Victorina est au balcon.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1536,7 +1594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Daphné a les pieds au sol. Elle est derrière la protection. Maman, l'adulte, est là.</t>
+          <t>Victorina a les pieds au sol. Elle est derrière la protection. Tu es avec l'adulte. Bravo, Victorina. Pieds au sol. Avec maman. Oui. C'est du bon travail. Tu restes derrière la protection ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1684,7 +1742,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Daphné a les pieds au sol. Elle est derrière la protection. Maman, l'adulte, est là.</t>
+          <t>narrateur|Victorina a les pieds au sol.
+narrateur|Elle est derrière la protection.
+maman|Tu es avec l'adulte.
+maman|Bravo, Victorina.
+enfant-f|Pieds au sol.
+enfant-f|Avec maman.
+maman|Oui.
+maman|C'est du bon travail.
+maman|Tu restes derrière la protection ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1712,7 +1779,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Daphné et maman rentrent. Les pieds restent au sol.</t>
+          <t>Victorina et maman rentrent. Les pieds restent au sol. Le carrelage est encore tiède. On laisse le papillon dehors ? Oui. Tu as les pieds au sol, encore. Bravo. Les fleurs sont roses. On les a regardées ensemble. Derrière la protection. Tu veux t'asseoir sur le tapis ? Oui, maman. Le tapis est doux, tout chaud. On était avec l'adulte. Tes pieds sont au sol, ici aussi. Oui, maman.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1856,7 +1923,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Daphné et maman rentrent. Les pieds restent au sol.</t>
+          <t>narrateur|Victorina et maman rentrent.
+narrateur|Les pieds restent au sol.
+narrateur|Le carrelage est encore tiède.
+maman|On laisse le papillon dehors ?
+enfant-f|Oui.
+maman|Tu as les pieds au sol, encore.
+maman|Bravo.
+enfant-f|Les fleurs sont roses.
+maman|On les a regardées ensemble.
+maman|Derrière la protection.
+maman|Tu veux t'asseoir sur le tapis ?
+enfant-f|Oui, maman.
+narrateur|Le tapis est doux, tout chaud.
+maman|On était avec l'adulte.
+maman|Tes pieds sont au sol, ici aussi.
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1884,7 +1966,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'avais les pieds au sol. Avec maman. Bravo. Tu as fait du bon travail. Les géraniums restent roses. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2024,7 +2106,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'avais les pieds au sol.
+enfant-f|Avec maman.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Les géraniums restent roses.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2046,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2084,6 +2171,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-05.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le carrelage du salon est tiède. Le soleil a tout chauffé, tout doux. Une poussière d'or danse dans le rayon. Ça sent les géraniums, déjà. Les pots sont roses, près de la vitre. Une feuille a une petite goutte. Un grain de pollen brille, tout fin. Le rayon est jaune, tout chaud. Tu as senti les fleurs, Victorina ? Oui, maman. Ça sent fort. Les géraniums sont roses, aujourd'hui. En ce moment, maman ouvre la porte. L'air sent les géraniums, plus près. Victorina reste avec l'adulte. C'est maman. On reste derrière la protection. D'accord, maman. Victorina pose les pieds au sol. Les pieds restent au sol. Elle sent le carrelage sous les chaussettes. La protection est devant elle. Victorina pose les mains sur la protection. Elle reste derrière la protection. Bravo, Victorina. Tes pieds sont au sol. Un papillon passe, tout léger. Maman, le papillon. Je le vois. On le regarde ici, avec moi. Maman est près d'elle. Parce que les pieds sont au sol, Victorina est calme. Elles regardent les pots. Les fleurs sont roses. Les pieds restent au sol. Tu vois les pétales ? Oui. Ils sont roses. On reste avec l'adulte. Derrière la protection. Pieds au sol. Oui. C'est du bon travail. Tu as fini de regarder le papillon ? Il est encore là. Alors on reste un peu. Tu vois les pots roses ? Un, deux, trois. On les compte ici. Derrière la protection.</t>
+          <t>Le carrelage du salon est tiède. Le soleil a tout chauffé, tout doux. Une poussière d'or danse dans le rayon. Ça sent les géraniums, déjà. Les pots sont roses, près de la vitre. Une feuille a une petite goutte. Un grain de pollen brille, tout fin. Le rayon est jaune, tout chaud. Tu as senti les fleurs, Victorina ? Oui, maman. Ça sent fort. Les géraniums sont roses, aujourd'hui. En ce moment, maman ouvre la porte. L'air sent les géraniums, plus près. Victorina reste avec l'adulte. C'est maman. On reste derrière la protection. D'accord, maman. Victorina pose les pieds au sol. Les pieds restent au sol. Elle sent le carrelage sous les chaussettes. La protection est devant elle. Victorina pose les mains sur la protection. Elle reste derrière la protection. Bravo, Victorina. Tes pieds sont au sol. Un papillon passe, tout léger. Maman, le papillon. Je le vois. On le regarde ici, avec moi. Maman est près d'elle. Parce que les pieds sont au sol, Victorina est calme. Elles regardent les pots. Les fleurs sont roses. Les pieds restent au sol. Tu vois les pétales ? Oui. Ils sont roses. On reste avec l'adulte. Derrière la protection. Pieds au sol. Oui. Tu as fini de regarder le papillon ? Il est encore là. Alors on reste un peu. Tu vois les pots roses ? Un, deux, trois. On les compte ici. Derrière la protection.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Daphné est à la maison. Maman ouvre la porte du balcon. L'air sent les géraniums. Daphné reste avec l'adulte. C'est maman. Maman dit : on reste derrière la protection. Daphné pose les &lt;emphasis level="moderate"&gt;pieds&lt;/emphasis&gt; au sol. Les pieds restent au sol. Elle sent le carrelage sous les chaussettes. La protection est devant elle. Daphné pose les mains sur la protection. Elle reste derrière la protection. Un papillon passe. Daphné dit : maman, le papillon. Maman est près d'elle. Parce que les pieds sont au sol, Daphné est calme. Elles regardent les pots. Les fleurs sont roses. Les pieds restent au sol. L'adulte est là.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le carrelage du salon est tiède. Le soleil a tout chauffé, tout doux. Une poussière d'or danse dans le rayon. Ça sent les géraniums, déjà. Les pots sont roses, près de la vitre. Une feuille a une petite goutte. Un grain de pollen brille, tout fin. Le rayon est jaune, tout chaud. Tu as senti les fleurs, Victorina ? Oui, maman. Ça sent fort. Les géraniums sont roses, aujourd'hui. En ce moment, maman ouvre la porte. L'air sent les géraniums, plus près. Victorina reste avec l'adulte. C'est maman. On reste derrière la protection. D'accord, maman. Victorina pose les pieds au sol. Les pieds restent au sol. Elle sent le carrelage sous les chaussettes. La protection est devant elle. Victorina pose les mains sur la protection. Elle reste derrière la protection. Bravo, Victorina. Tes pieds sont au sol. Un papillon passe, tout léger. Maman, le papillon. Je le vois. On le regarde ici, avec moi. Maman est près d'elle. Parce que les pieds sont au sol, Victorina est calme. Elles regardent les pots. Les fleurs sont roses. Les pieds restent au sol. Tu vois les pétales ? Oui. Ils sont roses. On reste avec l'adulte. Derrière la protection. Pieds au sol. Oui. Tu as fini de regarder le papillon ? Il est encore là. Alors on reste un peu. Tu vois les pots roses ? Un, deux, trois. On les compte ici. Derrière la protection.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1366,7 +1366,6 @@
 maman|Derrière la protection.
 enfant-f|Pieds au sol.
 maman|Oui.
-maman|C'est du bon travail.
 maman|Tu as fini de regarder le papillon ?
 enfant-f|Il est encore là.
 maman|Alors on reste un peu.
@@ -1410,7 +1409,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Daphné est au balcon. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina est au balcon. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1569,7 +1568,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1594,12 +1592,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a les pieds au sol. Elle est derrière la protection. Tu es avec l'adulte. Bravo, Victorina. Pieds au sol. Avec maman. Oui. C'est du bon travail. Tu restes derrière la protection ? Oui, maman.</t>
+          <t>Victorina a les pieds au sol. Elle est derrière la protection. Tu es avec l'adulte. Bravo, Victorina. Pieds au sol. Avec maman. Oui. Tu restes derrière la protection ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Daphné a les &lt;emphasis level="moderate"&gt;pieds&lt;/emphasis&gt; au sol. Elle est derrière la protection. Maman, l'adulte, est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a les pieds au sol. Elle est derrière la protection. Tu es avec l'adulte. Bravo, Victorina. Pieds au sol. Avec maman. Oui. Tu restes derrière la protection ? Oui, maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1749,12 +1747,10 @@
 enfant-f|Pieds au sol.
 enfant-f|Avec maman.
 maman|Oui.
-maman|C'est du bon travail.
 maman|Tu restes derrière la protection ?
 enfant-f|Oui, maman.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1784,7 +1780,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Daphné et maman rentrent. Les &lt;emphasis level="moderate"&gt;pieds&lt;/emphasis&gt; restent au sol.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina et maman rentrent. Les pieds restent au sol. Le carrelage est encore tiède. On laisse le papillon dehors ? Oui. Tu as les pieds au sol, encore. Bravo. Les fleurs sont roses. On les a regardées ensemble. Derrière la protection. Tu veux t'asseoir sur le tapis ? Oui, maman. Le tapis est doux, tout chaud. On était avec l'adulte. Tes pieds sont au sol, ici aussi. Oui, maman.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1941,7 +1937,6 @@
 enfant-f|Oui, maman.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1966,12 +1961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'avais les pieds au sol. Avec maman. Bravo. Tu as fait du bon travail. Les géraniums restent roses. L'histoire est finie.</t>
+          <t>J'avais les pieds au sol. Avec maman. Bravo. Les géraniums restent roses.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'avais les pieds au sol. Avec maman. Bravo. Les géraniums restent roses.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2109,12 +2104,9 @@
           <t>enfant-f|J'avais les pieds au sol.
 enfant-f|Avec maman.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Les géraniums restent roses.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Les géraniums restent roses.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2133,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2178,6 +2170,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-05.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Daphné, maman</t>
+          <t>Victorina, maman</t>
         </is>
       </c>
     </row>
